--- a/web/public/forms/heulmagi-sigong.xlsx
+++ b/web/public/forms/heulmagi-sigong.xlsx
@@ -977,7 +977,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="76" t="inlineStr">
@@ -2944,7 +2944,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="76" t="inlineStr">
@@ -3368,7 +3368,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="76" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="76" t="inlineStr">
@@ -4383,7 +4383,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="76" t="inlineStr">
@@ -6291,7 +6291,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="J1" s="76" t="inlineStr">
@@ -7000,7 +7000,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11776,7 +11776,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">

--- a/web/public/forms/heulmagi-sigong.xlsx
+++ b/web/public/forms/heulmagi-sigong.xlsx
@@ -910,7 +910,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
